--- a/Result/profitability/1586.xlsx
+++ b/Result/profitability/1586.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM70"/>
+  <dimension ref="A1:AM71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.75</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07124999999999999</v>
+        <v>0.08875</v>
       </c>
       <c r="N2" t="n">
-        <v>14.88</v>
+        <v>14.93875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.45</v>
       </c>
       <c r="M3" t="n">
-        <v>0.25125</v>
+        <v>0.26875</v>
       </c>
       <c r="N3" t="n">
-        <v>15.61625</v>
+        <v>15.73625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0.35</v>
+        <v>0.41</v>
       </c>
       <c r="N4" t="n">
-        <v>16.415</v>
+        <v>16.925</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>2.53</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7075</v>
+        <v>0.74</v>
       </c>
       <c r="N5" t="n">
-        <v>18.89</v>
+        <v>19.335</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.62</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9237500000000001</v>
+        <v>0.9475</v>
       </c>
       <c r="N6" t="n">
-        <v>20.0875</v>
+        <v>20.4775</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1161,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" t="n">
         <v>99.09999999999999</v>
@@ -1264,10 +1264,10 @@
         <v>1.27</v>
       </c>
       <c r="M7" t="n">
-        <v>1.0875</v>
+        <v>1.0925</v>
       </c>
       <c r="N7" t="n">
-        <v>22.685</v>
+        <v>22.81125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>1.11</v>
+        <v>1.1075</v>
       </c>
       <c r="N8" t="n">
-        <v>19.755</v>
+        <v>19.43</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9322,6 +9322,133 @@
       </c>
       <c r="AM70" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1586</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>621</v>
+      </c>
+      <c r="D71" t="n">
+        <v>527</v>
+      </c>
+      <c r="E71" t="n">
+        <v>94</v>
+      </c>
+      <c r="F71" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="G71" t="n">
+        <v>15</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2.49%</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>17</v>
+      </c>
+      <c r="K71" t="n">
+        <v>15</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M71" t="n">
+        <v>-0.003750000000000007</v>
+      </c>
+      <c r="N71" t="n">
+        <v>13.815</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W71" t="n">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="X71" t="n">
+        <v>-0.1176470588235295</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>-2.599999999999998</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>-0.1465614430665162</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>-2.363636363636363</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>0.3074265975820381</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK71" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
